--- a/Results_experiment/exp_4/preds_1114422222322222.xlsx
+++ b/Results_experiment/exp_4/preds_1114422222322222.xlsx
@@ -1245,7 +1245,7 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>0.9632883071899414</v>
+        <v>1.765547513961792</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1259,7 +1259,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D3">
-        <v>2.125311374664307</v>
+        <v>2.175282955169678</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1273,7 +1273,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>1.781115651130676</v>
+        <v>3.998681306838989</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1287,7 +1287,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D5">
-        <v>1.167442560195923</v>
+        <v>2.378461837768555</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1301,7 +1301,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D6">
-        <v>1.162431240081787</v>
+        <v>4.861313819885254</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1315,7 +1315,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D7">
-        <v>1.766842842102051</v>
+        <v>2.022732973098755</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1329,7 +1329,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D8">
-        <v>3.9956955909729</v>
+        <v>3.98108434677124</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1343,7 +1343,7 @@
         <v>4.5</v>
       </c>
       <c r="D9">
-        <v>1.85470712184906</v>
+        <v>2.446765422821045</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1357,7 +1357,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D10">
-        <v>1.159917712211609</v>
+        <v>1.314471483230591</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1371,7 +1371,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D11">
-        <v>1.34725821018219</v>
+        <v>2.710104942321777</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1385,7 +1385,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D12">
-        <v>1.099191546440125</v>
+        <v>0.8947309255599976</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1399,7 +1399,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D13">
-        <v>1.055395364761353</v>
+        <v>1.14706027507782</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1413,7 +1413,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D14">
-        <v>1.091895699501038</v>
+        <v>1.285972833633423</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1427,7 +1427,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D15">
-        <v>2.601150751113892</v>
+        <v>3.363378763198853</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1441,7 +1441,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D16">
-        <v>2.856888294219971</v>
+        <v>2.91376256942749</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1455,7 +1455,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D17">
-        <v>2.331273555755615</v>
+        <v>2.212730646133423</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1469,7 +1469,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D18">
-        <v>1.189618110656738</v>
+        <v>1.022234916687012</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1483,7 +1483,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D19">
-        <v>1.936484098434448</v>
+        <v>2.668669939041138</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1497,7 +1497,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D20">
-        <v>2.641237020492554</v>
+        <v>2.770164012908936</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1511,7 +1511,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D21">
-        <v>0.9526187181472778</v>
+        <v>1.290230751037598</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1525,7 +1525,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D22">
-        <v>4.176312446594238</v>
+        <v>3.78976845741272</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1539,7 +1539,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D23">
-        <v>2.934555530548096</v>
+        <v>2.488781929016113</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1553,7 +1553,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D24">
-        <v>2.813742637634277</v>
+        <v>3.064409971237183</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1567,7 +1567,7 @@
         <v>0.5</v>
       </c>
       <c r="D25">
-        <v>2.017241954803467</v>
+        <v>1.952486276626587</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1581,7 +1581,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D26">
-        <v>1.654340505599976</v>
+        <v>4.220261096954346</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1595,7 +1595,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D27">
-        <v>1.746097803115845</v>
+        <v>2.280541896820068</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1609,7 +1609,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D28">
-        <v>1.226477861404419</v>
+        <v>1.330506563186646</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1623,7 +1623,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D29">
-        <v>1.595650434494019</v>
+        <v>1.533078908920288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1637,7 +1637,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D30">
-        <v>1.294690847396851</v>
+        <v>0.7836625576019287</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1651,7 +1651,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D31">
-        <v>3.586320638656616</v>
+        <v>4.247185707092285</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1665,7 +1665,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D32">
-        <v>4.091475486755371</v>
+        <v>9.028471946716309</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1679,7 +1679,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D33">
-        <v>1.483744978904724</v>
+        <v>3.68884801864624</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1693,7 +1693,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D34">
-        <v>0.9855248928070068</v>
+        <v>0.816741943359375</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1707,7 +1707,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D35">
-        <v>1.252638697624207</v>
+        <v>1.272543668746948</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1721,7 +1721,7 @@
         <v>19.20000076293945</v>
       </c>
       <c r="D36">
-        <v>11.83866024017334</v>
+        <v>15.63930892944336</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1735,7 +1735,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D37">
-        <v>2.224777221679688</v>
+        <v>2.229821920394897</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1749,7 +1749,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D38">
-        <v>2.049198627471924</v>
+        <v>2.207730770111084</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1763,7 +1763,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D39">
-        <v>2.388365745544434</v>
+        <v>2.298689842224121</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1777,7 +1777,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D40">
-        <v>0.9586055278778076</v>
+        <v>0.86143958568573</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1791,7 +1791,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D41">
-        <v>0.9357413649559021</v>
+        <v>0.7820160984992981</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1805,7 +1805,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D42">
-        <v>3.753511667251587</v>
+        <v>3.456578969955444</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1819,7 +1819,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D43">
-        <v>0.9650708436965942</v>
+        <v>0.7744696140289307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1833,7 +1833,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D44">
-        <v>4.0203857421875</v>
+        <v>3.330454111099243</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1847,7 +1847,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D45">
-        <v>1.202621459960938</v>
+        <v>1.303576946258545</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1861,7 +1861,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D46">
-        <v>1.503055334091187</v>
+        <v>1.627918481826782</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1875,7 +1875,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D47">
-        <v>1.085771560668945</v>
+        <v>0.9767853021621704</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1889,7 +1889,7 @@
         <v>3.5</v>
       </c>
       <c r="D48">
-        <v>2.59880256652832</v>
+        <v>3.10888671875</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1903,7 +1903,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D49">
-        <v>3.096442699432373</v>
+        <v>3.322105646133423</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1917,7 +1917,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D50">
-        <v>2.769275188446045</v>
+        <v>3.588692426681519</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1931,7 +1931,7 @@
         <v>2</v>
       </c>
       <c r="D51">
-        <v>1.23817253112793</v>
+        <v>1.307920217514038</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1945,7 +1945,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D52">
-        <v>0.9744340181350708</v>
+        <v>0.8986874222755432</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1959,7 +1959,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>0.969641387462616</v>
+        <v>1.745925664901733</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1973,7 +1973,7 @@
         <v>2.5</v>
       </c>
       <c r="D54">
-        <v>2.749895334243774</v>
+        <v>2.245715856552124</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1987,7 +1987,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D55">
-        <v>1.579504251480103</v>
+        <v>2.481661558151245</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2001,7 +2001,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D56">
-        <v>2.242186307907104</v>
+        <v>3.059729814529419</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2015,7 +2015,7 @@
         <v>10.19999980926514</v>
       </c>
       <c r="D57">
-        <v>6.759012222290039</v>
+        <v>5.292685985565186</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2029,7 +2029,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D58">
-        <v>1.08945906162262</v>
+        <v>2.149652004241943</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2043,7 +2043,7 @@
         <v>2.5</v>
       </c>
       <c r="D59">
-        <v>1.437630176544189</v>
+        <v>1.296306371688843</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2057,7 +2057,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D60">
-        <v>3.353555917739868</v>
+        <v>6.28431510925293</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2071,7 +2071,7 @@
         <v>0.5</v>
       </c>
       <c r="D61">
-        <v>1.178826808929443</v>
+        <v>1.229079008102417</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2085,7 +2085,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D62">
-        <v>5.848869800567627</v>
+        <v>6.725185394287109</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2099,7 +2099,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D63">
-        <v>1.246168851852417</v>
+        <v>1.038826942443848</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2113,7 +2113,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D64">
-        <v>1.09893524646759</v>
+        <v>0.805182933807373</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2127,7 +2127,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D65">
-        <v>0.8995873928070068</v>
+        <v>1.610743880271912</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2141,7 +2141,7 @@
         <v>1.5</v>
       </c>
       <c r="D66">
-        <v>2.278439521789551</v>
+        <v>2.125475168228149</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2155,7 +2155,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D67">
-        <v>2.58004355430603</v>
+        <v>3.174688100814819</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2169,7 +2169,7 @@
         <v>5.5</v>
       </c>
       <c r="D68">
-        <v>2.8551926612854</v>
+        <v>3.941442489624023</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2183,7 +2183,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D69">
-        <v>0.9376851320266724</v>
+        <v>1.353269100189209</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2197,7 +2197,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D70">
-        <v>2.383224725723267</v>
+        <v>2.6184401512146</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2211,7 +2211,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D71">
-        <v>2.088198661804199</v>
+        <v>1.576643705368042</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2225,7 +2225,7 @@
         <v>3.5</v>
       </c>
       <c r="D72">
-        <v>4.118388175964355</v>
+        <v>5.986948013305664</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2239,7 +2239,7 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>1.270869731903076</v>
+        <v>1.212194919586182</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2253,7 +2253,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D74">
-        <v>1.758766174316406</v>
+        <v>1.614548325538635</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2267,7 +2267,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D75">
-        <v>6.008111953735352</v>
+        <v>5.217618942260742</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2281,7 +2281,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D76">
-        <v>1.170287132263184</v>
+        <v>1.403849959373474</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2295,7 +2295,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D77">
-        <v>2.907544851303101</v>
+        <v>2.192550420761108</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2309,7 +2309,7 @@
         <v>2</v>
       </c>
       <c r="D78">
-        <v>2.996560573577881</v>
+        <v>2.741997003555298</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2323,7 +2323,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D79">
-        <v>3.525341987609863</v>
+        <v>3.654119491577148</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2337,7 +2337,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D80">
-        <v>1.816742658615112</v>
+        <v>4.127575397491455</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2351,7 +2351,7 @@
         <v>7</v>
       </c>
       <c r="D81">
-        <v>3.287381887435913</v>
+        <v>1.548717021942139</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2365,7 +2365,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D82">
-        <v>0.9483435153961182</v>
+        <v>0.7854068875312805</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2379,7 +2379,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D83">
-        <v>2.530554294586182</v>
+        <v>2.530045986175537</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2393,7 +2393,7 @@
         <v>1</v>
       </c>
       <c r="D84">
-        <v>3.701224565505981</v>
+        <v>5.820981979370117</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2407,7 +2407,7 @@
         <v>21</v>
       </c>
       <c r="D85">
-        <v>13.66651725769043</v>
+        <v>17.22710227966309</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2421,7 +2421,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D86">
-        <v>1.982152938842773</v>
+        <v>2.492571353912354</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2435,7 +2435,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D87">
-        <v>0.9547021389007568</v>
+        <v>0.7709532976150513</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2449,7 +2449,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D88">
-        <v>3.705399036407471</v>
+        <v>3.694342851638794</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2463,7 +2463,7 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>2.105749607086182</v>
+        <v>2.415091991424561</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2477,7 +2477,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D90">
-        <v>1.421056985855103</v>
+        <v>1.54767370223999</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2491,7 +2491,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D91">
-        <v>1.216593861579895</v>
+        <v>1.364413499832153</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2505,7 +2505,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D92">
-        <v>1.858315587043762</v>
+        <v>2.807691812515259</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2519,7 +2519,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D93">
-        <v>1.059536218643188</v>
+        <v>0.9306066036224365</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2533,7 +2533,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D94">
-        <v>1.228569507598877</v>
+        <v>1.34498143196106</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2547,7 +2547,7 @@
         <v>2</v>
       </c>
       <c r="D95">
-        <v>1.71708607673645</v>
+        <v>2.193075656890869</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2561,7 +2561,7 @@
         <v>1.5</v>
       </c>
       <c r="D96">
-        <v>0.9563276767730713</v>
+        <v>0.8654712438583374</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2575,7 +2575,7 @@
         <v>3</v>
       </c>
       <c r="D97">
-        <v>2.607129573822021</v>
+        <v>4.011776924133301</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2589,7 +2589,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D98">
-        <v>1.642385363578796</v>
+        <v>2.708565473556519</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2603,7 +2603,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D99">
-        <v>0.9840739965438843</v>
+        <v>0.8014518022537231</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2617,7 +2617,7 @@
         <v>0.5</v>
       </c>
       <c r="D100">
-        <v>0.9786626100540161</v>
+        <v>0.9545822143554688</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2631,7 +2631,7 @@
         <v>1.5</v>
       </c>
       <c r="D101">
-        <v>0.9722079038619995</v>
+        <v>1.065237164497375</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2645,7 +2645,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D102">
-        <v>3.274577617645264</v>
+        <v>1.276296615600586</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2659,7 +2659,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="D103">
-        <v>5.625041484832764</v>
+        <v>10.43487071990967</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2673,7 +2673,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D104">
-        <v>3.675031661987305</v>
+        <v>5.052931785583496</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2687,7 +2687,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D105">
-        <v>2.226747751235962</v>
+        <v>2.746319532394409</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2701,7 +2701,7 @@
         <v>2</v>
       </c>
       <c r="D106">
-        <v>2.26511812210083</v>
+        <v>2.289336919784546</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2715,7 +2715,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D107">
-        <v>1.064631700515747</v>
+        <v>1.607873558998108</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2729,7 +2729,7 @@
         <v>2.5</v>
       </c>
       <c r="D108">
-        <v>2.276465892791748</v>
+        <v>2.665878772735596</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2743,7 +2743,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D109">
-        <v>2.661646366119385</v>
+        <v>3.234667539596558</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2757,7 +2757,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D110">
-        <v>4.177793979644775</v>
+        <v>5.777143478393555</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2771,7 +2771,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D111">
-        <v>2.42731785774231</v>
+        <v>2.382023334503174</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2785,7 +2785,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D112">
-        <v>1.18608021736145</v>
+        <v>0.9119727611541748</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2799,7 +2799,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D113">
-        <v>1.264845371246338</v>
+        <v>1.092089176177979</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2813,7 +2813,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D114">
-        <v>2.198300361633301</v>
+        <v>2.37519383430481</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2827,7 +2827,7 @@
         <v>0.5</v>
       </c>
       <c r="D115">
-        <v>0.9335987567901611</v>
+        <v>1.945316076278687</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2841,7 +2841,7 @@
         <v>2</v>
       </c>
       <c r="D116">
-        <v>1.082122802734375</v>
+        <v>1.145881772041321</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2855,7 +2855,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D117">
-        <v>0.9954034686088562</v>
+        <v>1.305413246154785</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2869,7 +2869,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D118">
-        <v>3.29033374786377</v>
+        <v>5.031604290008545</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2883,7 +2883,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D119">
-        <v>0.9582793116569519</v>
+        <v>1.0353022813797</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2897,7 +2897,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D120">
-        <v>0.9475085735321045</v>
+        <v>0.7923611998558044</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2911,7 +2911,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D121">
-        <v>0.9188045263290405</v>
+        <v>1.293537616729736</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2925,7 +2925,7 @@
         <v>17.10000038146973</v>
       </c>
       <c r="D122">
-        <v>5.466894149780273</v>
+        <v>10.47566509246826</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2939,7 +2939,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D123">
-        <v>2.018385887145996</v>
+        <v>1.528173446655273</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2953,7 +2953,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D124">
-        <v>1.011993050575256</v>
+        <v>1.344416499137878</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2967,7 +2967,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D125">
-        <v>2.24910306930542</v>
+        <v>2.436598062515259</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2981,7 +2981,7 @@
         <v>18.29999923706055</v>
       </c>
       <c r="D126">
-        <v>12.01331806182861</v>
+        <v>14.04678058624268</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2995,7 +2995,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D127">
-        <v>2.187465667724609</v>
+        <v>3.376687288284302</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3009,7 +3009,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D128">
-        <v>1.238364696502686</v>
+        <v>1.122456908226013</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3023,7 +3023,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D129">
-        <v>1.978054523468018</v>
+        <v>1.98145580291748</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3037,7 +3037,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D130">
-        <v>2.204948663711548</v>
+        <v>2.161587715148926</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3051,7 +3051,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D131">
-        <v>1.212970495223999</v>
+        <v>1.220450639724731</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3065,7 +3065,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D132">
-        <v>2.031040668487549</v>
+        <v>2.827306747436523</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3079,7 +3079,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D133">
-        <v>3.147022724151611</v>
+        <v>6.691360473632812</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3093,7 +3093,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D134">
-        <v>0.970374584197998</v>
+        <v>0.7693055868148804</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3107,7 +3107,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D135">
-        <v>2.495859622955322</v>
+        <v>3.214047431945801</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3121,7 +3121,7 @@
         <v>17.29999923706055</v>
       </c>
       <c r="D136">
-        <v>5.526679039001465</v>
+        <v>4.506935596466064</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3135,7 +3135,7 @@
         <v>2.5</v>
       </c>
       <c r="D137">
-        <v>2.097607374191284</v>
+        <v>1.833382368087769</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3149,7 +3149,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D138">
-        <v>0.9362626075744629</v>
+        <v>0.9412932395935059</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3163,7 +3163,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D139">
-        <v>3.552928447723389</v>
+        <v>2.579959154129028</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3177,7 +3177,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D140">
-        <v>2.000885486602783</v>
+        <v>2.929938554763794</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3191,7 +3191,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D141">
-        <v>3.185442686080933</v>
+        <v>3.247810125350952</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3205,7 +3205,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D142">
-        <v>3.621262550354004</v>
+        <v>1.916017055511475</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3219,7 +3219,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D143">
-        <v>2.281578779220581</v>
+        <v>2.814965009689331</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3233,7 +3233,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D144">
-        <v>0.9310269355773926</v>
+        <v>1.179263353347778</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3247,7 +3247,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D145">
-        <v>0.9599912166595459</v>
+        <v>0.889495849609375</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3261,7 +3261,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D146">
-        <v>1.022840142250061</v>
+        <v>0.9639344811439514</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3275,7 +3275,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D147">
-        <v>2.41790246963501</v>
+        <v>2.24805474281311</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3289,7 +3289,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D148">
-        <v>2.441338062286377</v>
+        <v>2.652941226959229</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3303,7 +3303,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D149">
-        <v>2.099799633026123</v>
+        <v>1.605882883071899</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3317,7 +3317,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D150">
-        <v>2.22652268409729</v>
+        <v>2.195005178451538</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3331,7 +3331,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D151">
-        <v>2.478364229202271</v>
+        <v>2.183836698532104</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3345,7 +3345,7 @@
         <v>11</v>
       </c>
       <c r="D152">
-        <v>6.75441837310791</v>
+        <v>8.937922477722168</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3359,7 +3359,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D153">
-        <v>2.325318098068237</v>
+        <v>2.908624887466431</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3373,7 +3373,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D154">
-        <v>2.20880126953125</v>
+        <v>2.117281436920166</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3387,7 +3387,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D155">
-        <v>1.25184953212738</v>
+        <v>0.9535523653030396</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3401,7 +3401,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D156">
-        <v>1.072114706039429</v>
+        <v>1.077735424041748</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3415,7 +3415,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D157">
-        <v>3.036902904510498</v>
+        <v>3.098754167556763</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3429,7 +3429,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D158">
-        <v>2.933216094970703</v>
+        <v>3.077899694442749</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3443,7 +3443,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D159">
-        <v>1.686179399490356</v>
+        <v>2.174339771270752</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3457,7 +3457,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D160">
-        <v>2.304853439331055</v>
+        <v>2.519286632537842</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3471,7 +3471,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D161">
-        <v>1.267108678817749</v>
+        <v>2.788600921630859</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3485,7 +3485,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D162">
-        <v>4.158981323242188</v>
+        <v>3.914774417877197</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3499,7 +3499,7 @@
         <v>1.5</v>
       </c>
       <c r="D163">
-        <v>2.441534757614136</v>
+        <v>2.513933420181274</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3513,7 +3513,7 @@
         <v>0.5</v>
       </c>
       <c r="D164">
-        <v>1.371468305587769</v>
+        <v>2.999265909194946</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3527,7 +3527,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D165">
-        <v>0.9449325799942017</v>
+        <v>1.992567300796509</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3541,7 +3541,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D166">
-        <v>2.568912029266357</v>
+        <v>2.534414052963257</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3555,7 +3555,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D167">
-        <v>2.141624212265015</v>
+        <v>2.12804102897644</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3569,7 +3569,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D168">
-        <v>2.113444566726685</v>
+        <v>2.036114931106567</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3583,7 +3583,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D169">
-        <v>0.984169602394104</v>
+        <v>0.7673152089118958</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3597,7 +3597,7 @@
         <v>6</v>
       </c>
       <c r="D170">
-        <v>1.778756856918335</v>
+        <v>2.840596199035645</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3611,7 +3611,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D171">
-        <v>2.387502431869507</v>
+        <v>2.671275615692139</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3625,7 +3625,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D172">
-        <v>0.9474760293960571</v>
+        <v>0.8472599387168884</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3639,7 +3639,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D173">
-        <v>2.339894771575928</v>
+        <v>3.299987554550171</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3653,7 +3653,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D174">
-        <v>0.9216609001159668</v>
+        <v>1.298949003219604</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3667,7 +3667,7 @@
         <v>2.5</v>
       </c>
       <c r="D175">
-        <v>3.533212423324585</v>
+        <v>3.480068445205688</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3681,7 +3681,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D176">
-        <v>0.976900577545166</v>
+        <v>0.8034128546714783</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3695,7 +3695,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D177">
-        <v>2.821249961853027</v>
+        <v>2.427770853042603</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3709,7 +3709,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D178">
-        <v>1.421706199645996</v>
+        <v>1.482485055923462</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3723,7 +3723,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D179">
-        <v>2.668875932693481</v>
+        <v>3.214724540710449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3737,7 +3737,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D180">
-        <v>2.169390439987183</v>
+        <v>2.14054536819458</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3751,7 +3751,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D181">
-        <v>0.9594412446022034</v>
+        <v>0.7789276242256165</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3765,7 +3765,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D182">
-        <v>2.321465492248535</v>
+        <v>2.382442474365234</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3779,7 +3779,7 @@
         <v>0.5</v>
       </c>
       <c r="D183">
-        <v>1.177629590034485</v>
+        <v>1.224046468734741</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3793,7 +3793,7 @@
         <v>5</v>
       </c>
       <c r="D184">
-        <v>2.139257669448853</v>
+        <v>2.383461236953735</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3807,7 +3807,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D185">
-        <v>1.669286727905273</v>
+        <v>1.645298957824707</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3821,7 +3821,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D186">
-        <v>0.9712726473808289</v>
+        <v>1.060789108276367</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3835,7 +3835,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D187">
-        <v>0.9479485750198364</v>
+        <v>1.327602624893188</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3849,7 +3849,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D188">
-        <v>2.197894096374512</v>
+        <v>2.099354267120361</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3863,7 +3863,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D189">
-        <v>2.376332759857178</v>
+        <v>1.753469228744507</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3877,7 +3877,7 @@
         <v>6</v>
       </c>
       <c r="D190">
-        <v>2.519915342330933</v>
+        <v>3.332129240036011</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3891,7 +3891,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D191">
-        <v>3.594888210296631</v>
+        <v>4.258956432342529</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3905,7 +3905,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D192">
-        <v>1.129248857498169</v>
+        <v>1.300490140914917</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3919,7 +3919,7 @@
         <v>1.5</v>
       </c>
       <c r="D193">
-        <v>1.673964023590088</v>
+        <v>1.48943293094635</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3933,7 +3933,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D194">
-        <v>2.964799404144287</v>
+        <v>3.033860445022583</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3947,7 +3947,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D195">
-        <v>2.710330009460449</v>
+        <v>2.28807544708252</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3961,7 +3961,7 @@
         <v>4.099999904632568</v>
       </c>
       <c r="D196">
-        <v>2.170171737670898</v>
+        <v>2.201777458190918</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3975,7 +3975,7 @@
         <v>6.5</v>
       </c>
       <c r="D197">
-        <v>1.440762877464294</v>
+        <v>2.929977416992188</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3989,7 +3989,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D198">
-        <v>3.649490833282471</v>
+        <v>3.459665060043335</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="D199">
-        <v>1.244756937026978</v>
+        <v>1.385881900787354</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4017,7 +4017,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D200">
-        <v>0.9206993579864502</v>
+        <v>1.326628923416138</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4031,7 +4031,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D201">
-        <v>2.108798742294312</v>
+        <v>2.17865514755249</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4045,7 +4045,7 @@
         <v>5.5</v>
       </c>
       <c r="D202">
-        <v>3.565667867660522</v>
+        <v>4.016616821289062</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4059,7 +4059,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D203">
-        <v>1.089081764221191</v>
+        <v>1.996902704238892</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4073,7 +4073,7 @@
         <v>1.5</v>
       </c>
       <c r="D204">
-        <v>3.613992691040039</v>
+        <v>2.884891748428345</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4087,7 +4087,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D205">
-        <v>4.696154117584229</v>
+        <v>3.158772230148315</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4101,7 +4101,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D206">
-        <v>0.9149891138076782</v>
+        <v>2.103993654251099</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4115,7 +4115,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D207">
-        <v>3.079255104064941</v>
+        <v>2.865333795547485</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="D208">
-        <v>0.9609007239341736</v>
+        <v>0.9148882627487183</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4143,7 +4143,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D209">
-        <v>2.098381042480469</v>
+        <v>1.4645836353302</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4157,7 +4157,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D210">
-        <v>1.224793314933777</v>
+        <v>1.326553583145142</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4171,7 +4171,7 @@
         <v>2</v>
       </c>
       <c r="D211">
-        <v>2.46727728843689</v>
+        <v>2.37861704826355</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4185,7 +4185,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D212">
-        <v>3.58607006072998</v>
+        <v>6.181790351867676</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4199,7 +4199,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D213">
-        <v>1.817522048950195</v>
+        <v>2.544249296188354</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4213,7 +4213,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D214">
-        <v>2.935106039047241</v>
+        <v>3.183411836624146</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4227,7 +4227,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D215">
-        <v>4.75593376159668</v>
+        <v>4.162919998168945</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4241,7 +4241,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D216">
-        <v>3.055741786956787</v>
+        <v>3.642695426940918</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4255,7 +4255,7 @@
         <v>9</v>
       </c>
       <c r="D217">
-        <v>3.390347719192505</v>
+        <v>5.04950475692749</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4269,7 +4269,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D218">
-        <v>3.894245624542236</v>
+        <v>5.731551647186279</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4283,7 +4283,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D219">
-        <v>3.648665904998779</v>
+        <v>3.676409244537354</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4297,7 +4297,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D220">
-        <v>1.775848150253296</v>
+        <v>2.077100992202759</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4311,7 +4311,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D221">
-        <v>1.57710587978363</v>
+        <v>1.773277997970581</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4325,7 +4325,7 @@
         <v>3.5</v>
       </c>
       <c r="D222">
-        <v>1.154464960098267</v>
+        <v>1.345864295959473</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4339,7 +4339,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D223">
-        <v>1.948448181152344</v>
+        <v>1.043330192565918</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4353,7 +4353,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D224">
-        <v>3.125223159790039</v>
+        <v>2.898927688598633</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4367,7 +4367,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D225">
-        <v>1.157784104347229</v>
+        <v>1.315077781677246</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4381,7 +4381,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D226">
-        <v>0.9424669742584229</v>
+        <v>0.9940364956855774</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4395,7 +4395,7 @@
         <v>3.5</v>
       </c>
       <c r="D227">
-        <v>2.182225227355957</v>
+        <v>2.715271949768066</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4409,7 +4409,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D228">
-        <v>1.101126909255981</v>
+        <v>1.983591079711914</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4423,7 +4423,7 @@
         <v>11</v>
       </c>
       <c r="D229">
-        <v>3.376969337463379</v>
+        <v>7.437187194824219</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4437,7 +4437,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D230">
-        <v>2.965875148773193</v>
+        <v>3.165728807449341</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4451,7 +4451,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D231">
-        <v>2.114981889724731</v>
+        <v>2.49188494682312</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4465,7 +4465,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D232">
-        <v>2.496591806411743</v>
+        <v>4.210770606994629</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4479,7 +4479,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D233">
-        <v>0.9637689590454102</v>
+        <v>1.119401693344116</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4493,7 +4493,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D234">
-        <v>2.730684518814087</v>
+        <v>2.459537029266357</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4507,7 +4507,7 @@
         <v>0.5</v>
       </c>
       <c r="D235">
-        <v>2.17832088470459</v>
+        <v>1.956544876098633</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4521,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="D236">
-        <v>1.776612162590027</v>
+        <v>2.405348539352417</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4535,7 +4535,7 @@
         <v>0.5</v>
       </c>
       <c r="D237">
-        <v>0.9965214729309082</v>
+        <v>1.57643723487854</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4549,7 +4549,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D238">
-        <v>2.249846458435059</v>
+        <v>3.419896125793457</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4563,7 +4563,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D239">
-        <v>4.500936031341553</v>
+        <v>2.848408460617065</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4577,7 +4577,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D240">
-        <v>2.926748514175415</v>
+        <v>2.59857964515686</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4591,7 +4591,7 @@
         <v>6.699999809265137</v>
       </c>
       <c r="D241">
-        <v>3.148467540740967</v>
+        <v>2.734199285507202</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4605,7 +4605,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D242">
-        <v>3.580479621887207</v>
+        <v>2.869128227233887</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4619,7 +4619,7 @@
         <v>3.5</v>
       </c>
       <c r="D243">
-        <v>2.328295946121216</v>
+        <v>2.522722721099854</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4633,7 +4633,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D244">
-        <v>3.429351568222046</v>
+        <v>3.762489080429077</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4647,7 +4647,7 @@
         <v>2</v>
       </c>
       <c r="D245">
-        <v>0.9416412115097046</v>
+        <v>0.8450791239738464</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4661,7 +4661,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D246">
-        <v>3.475377321243286</v>
+        <v>3.558181524276733</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="D247">
-        <v>0.9486106038093567</v>
+        <v>0.7757338881492615</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4689,7 +4689,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D248">
-        <v>3.942018270492554</v>
+        <v>3.272940397262573</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4703,7 +4703,7 @@
         <v>20.5</v>
       </c>
       <c r="D249">
-        <v>0.9553376436233521</v>
+        <v>1.276543855667114</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4717,7 +4717,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D250">
-        <v>3.78143835067749</v>
+        <v>1.716283082962036</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4731,7 +4731,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D251">
-        <v>2.089898586273193</v>
+        <v>3.088518857955933</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4745,7 +4745,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D252">
-        <v>2.414188385009766</v>
+        <v>2.348166227340698</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4759,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="D253">
-        <v>2.853914737701416</v>
+        <v>3.275139570236206</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4773,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="D254">
-        <v>0.9479434490203857</v>
+        <v>0.8634443283081055</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4787,7 +4787,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D255">
-        <v>2.65460205078125</v>
+        <v>2.273378610610962</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4801,7 +4801,7 @@
         <v>11.39999961853027</v>
       </c>
       <c r="D256">
-        <v>3.544687509536743</v>
+        <v>4.685449600219727</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4815,7 +4815,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D257">
-        <v>3.263126850128174</v>
+        <v>5.474698543548584</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4829,7 +4829,7 @@
         <v>10.5</v>
       </c>
       <c r="D258">
-        <v>3.555678844451904</v>
+        <v>4.327112674713135</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4843,7 +4843,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D259">
-        <v>2.715000629425049</v>
+        <v>3.128397464752197</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4857,7 +4857,7 @@
         <v>1.5</v>
       </c>
       <c r="D260">
-        <v>2.543946981430054</v>
+        <v>1.995250225067139</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4871,7 +4871,7 @@
         <v>0.5</v>
       </c>
       <c r="D261">
-        <v>0.9619414806365967</v>
+        <v>0.8916674852371216</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4885,7 +4885,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D262">
-        <v>0.9112702608108521</v>
+        <v>1.450722932815552</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4899,7 +4899,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D263">
-        <v>0.9779374599456787</v>
+        <v>2.232606172561646</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4913,7 +4913,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D264">
-        <v>0.9748104810714722</v>
+        <v>0.7693049907684326</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4927,7 +4927,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D265">
-        <v>1.898059368133545</v>
+        <v>2.727502584457397</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4941,7 +4941,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D266">
-        <v>0.9353047609329224</v>
+        <v>0.8201724886894226</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4955,7 +4955,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D267">
-        <v>2.361260175704956</v>
+        <v>2.422219276428223</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4969,7 +4969,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D268">
-        <v>2.135039806365967</v>
+        <v>2.848689317703247</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4983,7 +4983,7 @@
         <v>7.599999904632568</v>
       </c>
       <c r="D269">
-        <v>6.267752647399902</v>
+        <v>7.467067718505859</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4997,7 +4997,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D270">
-        <v>1.36341392993927</v>
+        <v>1.798891067504883</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -5011,7 +5011,7 @@
         <v>2.5</v>
       </c>
       <c r="D271">
-        <v>2.115000247955322</v>
+        <v>2.17975902557373</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -5025,7 +5025,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D272">
-        <v>2.12148904800415</v>
+        <v>1.753419160842896</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -5039,7 +5039,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D273">
-        <v>2.839347839355469</v>
+        <v>3.120802164077759</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -5053,7 +5053,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D274">
-        <v>2.465767621994019</v>
+        <v>2.346299886703491</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5067,7 +5067,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D275">
-        <v>1.077481389045715</v>
+        <v>1.386524319648743</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5081,7 +5081,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D276">
-        <v>1.254287481307983</v>
+        <v>1.362504482269287</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5095,7 +5095,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D277">
-        <v>2.545661449432373</v>
+        <v>3.052852392196655</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5109,7 +5109,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D278">
-        <v>1.987927913665771</v>
+        <v>2.470417022705078</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5123,7 +5123,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D279">
-        <v>0.9854285717010498</v>
+        <v>0.7912333011627197</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5137,7 +5137,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D280">
-        <v>2.425329208374023</v>
+        <v>2.465853691101074</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5151,7 +5151,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D281">
-        <v>2.286526679992676</v>
+        <v>2.320994138717651</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5165,7 +5165,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D282">
-        <v>2.700071334838867</v>
+        <v>2.350208282470703</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5179,7 +5179,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D283">
-        <v>3.70555305480957</v>
+        <v>4.094104766845703</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5193,7 +5193,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D284">
-        <v>2.617140769958496</v>
+        <v>2.174381732940674</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5207,7 +5207,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D285">
-        <v>1.178966522216797</v>
+        <v>1.027943134307861</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5221,7 +5221,7 @@
         <v>2.5</v>
       </c>
       <c r="D286">
-        <v>2.51824426651001</v>
+        <v>2.335566520690918</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5235,7 +5235,7 @@
         <v>1</v>
       </c>
       <c r="D287">
-        <v>0.9593323469161987</v>
+        <v>0.7850112915039062</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5249,7 +5249,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D288">
-        <v>1.225597143173218</v>
+        <v>1.300220012664795</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5263,7 +5263,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D289">
-        <v>2.500972747802734</v>
+        <v>2.251352787017822</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5277,7 +5277,7 @@
         <v>0</v>
       </c>
       <c r="D290">
-        <v>0.9500352740287781</v>
+        <v>1.302923917770386</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5291,7 +5291,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D291">
-        <v>0.8732601404190063</v>
+        <v>1.602716684341431</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5305,7 +5305,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D292">
-        <v>1.207331657409668</v>
+        <v>1.237847805023193</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5319,7 +5319,7 @@
         <v>13.5</v>
       </c>
       <c r="D293">
-        <v>3.352616548538208</v>
+        <v>15.15498447418213</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5333,7 +5333,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D294">
-        <v>3.464711427688599</v>
+        <v>3.953607559204102</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5347,7 +5347,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D295">
-        <v>6.627490997314453</v>
+        <v>10.14143085479736</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5361,7 +5361,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D296">
-        <v>1.451420068740845</v>
+        <v>1.602569222450256</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5375,7 +5375,7 @@
         <v>5</v>
       </c>
       <c r="D297">
-        <v>2.234846830368042</v>
+        <v>2.157678604125977</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5389,7 +5389,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D298">
-        <v>2.105169773101807</v>
+        <v>1.715048789978027</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5403,7 +5403,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D299">
-        <v>2.020992755889893</v>
+        <v>2.158785104751587</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5417,7 +5417,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D300">
-        <v>3.556941986083984</v>
+        <v>3.51070761680603</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5431,7 +5431,7 @@
         <v>8</v>
       </c>
       <c r="D301">
-        <v>5.486625671386719</v>
+        <v>8.16411018371582</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5445,7 +5445,7 @@
         <v>0.5</v>
       </c>
       <c r="D302">
-        <v>3.539839744567871</v>
+        <v>3.413342237472534</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5459,7 +5459,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D303">
-        <v>2.227815628051758</v>
+        <v>2.730974674224854</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5473,7 +5473,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D304">
-        <v>0.9821518063545227</v>
+        <v>0.7929017543792725</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5487,7 +5487,7 @@
         <v>3</v>
       </c>
       <c r="D305">
-        <v>3.08957839012146</v>
+        <v>3.123882055282593</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5501,7 +5501,7 @@
         <v>5</v>
       </c>
       <c r="D306">
-        <v>1.837465405464172</v>
+        <v>2.174832344055176</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5515,7 +5515,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D307">
-        <v>2.935620307922363</v>
+        <v>2.495502471923828</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5529,7 +5529,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D308">
-        <v>1.997096538543701</v>
+        <v>2.535364627838135</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5543,7 +5543,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D309">
-        <v>3.021393775939941</v>
+        <v>3.407455205917358</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5557,7 +5557,7 @@
         <v>1.5</v>
       </c>
       <c r="D310">
-        <v>0.9622973799705505</v>
+        <v>0.7634266018867493</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5571,7 +5571,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D311">
-        <v>1.334781408309937</v>
+        <v>1.325861930847168</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5585,7 +5585,7 @@
         <v>0.5</v>
       </c>
       <c r="D312">
-        <v>0.9466277360916138</v>
+        <v>0.9837920665740967</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5599,7 +5599,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D313">
-        <v>1.007039189338684</v>
+        <v>1.94474983215332</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5613,7 +5613,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D314">
-        <v>1.062404155731201</v>
+        <v>1.377196073532104</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5627,7 +5627,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D315">
-        <v>1.586447477340698</v>
+        <v>2.115405082702637</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5641,7 +5641,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D316">
-        <v>1.00699770450592</v>
+        <v>2.252902984619141</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5655,7 +5655,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D317">
-        <v>4.926960945129395</v>
+        <v>5.0609130859375</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5669,7 +5669,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D318">
-        <v>3.774358749389648</v>
+        <v>5.176937103271484</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5683,7 +5683,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D319">
-        <v>3.064356327056885</v>
+        <v>3.216652631759644</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5697,7 +5697,7 @@
         <v>4</v>
       </c>
       <c r="D320">
-        <v>1.29511022567749</v>
+        <v>1.321469068527222</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5711,7 +5711,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D321">
-        <v>2.258846521377563</v>
+        <v>2.594449758529663</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5725,7 +5725,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D322">
-        <v>1.904481530189514</v>
+        <v>1.62885046005249</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5739,7 +5739,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D323">
-        <v>2.421156644821167</v>
+        <v>2.973497629165649</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5753,7 +5753,7 @@
         <v>2</v>
       </c>
       <c r="D324">
-        <v>1.157193183898926</v>
+        <v>1.397964715957642</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5767,7 +5767,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D325">
-        <v>1.98157787322998</v>
+        <v>1.576204538345337</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5781,7 +5781,7 @@
         <v>6</v>
       </c>
       <c r="D326">
-        <v>4.337551116943359</v>
+        <v>5.836074829101562</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5795,7 +5795,7 @@
         <v>1.5</v>
       </c>
       <c r="D327">
-        <v>0.9704803824424744</v>
+        <v>0.8664939999580383</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5809,7 +5809,7 @@
         <v>3.5</v>
       </c>
       <c r="D328">
-        <v>3.69067120552063</v>
+        <v>5.64861011505127</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5823,7 +5823,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D329">
-        <v>3.088816165924072</v>
+        <v>3.66032338142395</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5837,7 +5837,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D330">
-        <v>0.9160181283950806</v>
+        <v>1.650920391082764</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5851,7 +5851,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D331">
-        <v>2.921154499053955</v>
+        <v>2.911177396774292</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5865,7 +5865,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D332">
-        <v>2.239742517471313</v>
+        <v>2.181879281997681</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5879,7 +5879,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D333">
-        <v>0.8684310913085938</v>
+        <v>1.400443315505981</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5893,7 +5893,7 @@
         <v>7.5</v>
       </c>
       <c r="D334">
-        <v>3.663117408752441</v>
+        <v>4.944844245910645</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5907,7 +5907,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D335">
-        <v>1.177886247634888</v>
+        <v>1.041049957275391</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5921,7 +5921,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D336">
-        <v>3.062283754348755</v>
+        <v>3.258996963500977</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5935,7 +5935,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D337">
-        <v>0.9644898176193237</v>
+        <v>0.8479151725769043</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5949,7 +5949,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D338">
-        <v>1.873132586479187</v>
+        <v>2.10883641242981</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5963,7 +5963,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D339">
-        <v>0.9822181463241577</v>
+        <v>0.7876363396644592</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5977,7 +5977,7 @@
         <v>6.900000095367432</v>
       </c>
       <c r="D340">
-        <v>3.051724910736084</v>
+        <v>3.95694899559021</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5991,7 +5991,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D341">
-        <v>0.9441628456115723</v>
+        <v>2.193914890289307</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -6005,7 +6005,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D342">
-        <v>1.657970428466797</v>
+        <v>2.478862762451172</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -6019,7 +6019,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D343">
-        <v>1.237005114555359</v>
+        <v>1.388897657394409</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -6033,7 +6033,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D344">
-        <v>2.289111137390137</v>
+        <v>2.322795152664185</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -6047,7 +6047,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D345">
-        <v>2.260130405426025</v>
+        <v>2.080698490142822</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -6061,7 +6061,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D346">
-        <v>0.9077854752540588</v>
+        <v>1.613319754600525</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6075,7 +6075,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D347">
-        <v>3.518616676330566</v>
+        <v>5.154717445373535</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6089,7 +6089,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D348">
-        <v>2.857518434524536</v>
+        <v>2.92828106880188</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6103,7 +6103,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D349">
-        <v>3.27048134803772</v>
+        <v>3.174720525741577</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6117,7 +6117,7 @@
         <v>4</v>
       </c>
       <c r="D350">
-        <v>3.46702241897583</v>
+        <v>4.128565788269043</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6131,7 +6131,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D351">
-        <v>0.9800030589103699</v>
+        <v>1.136188507080078</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6145,7 +6145,7 @@
         <v>3</v>
       </c>
       <c r="D352">
-        <v>2.352400779724121</v>
+        <v>2.503705024719238</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6159,7 +6159,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D353">
-        <v>2.005978107452393</v>
+        <v>1.382099390029907</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6173,7 +6173,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D354">
-        <v>0.9597175717353821</v>
+        <v>0.8745478391647339</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6187,7 +6187,7 @@
         <v>4</v>
       </c>
       <c r="D355">
-        <v>3.303682804107666</v>
+        <v>3.59588623046875</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6201,7 +6201,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D356">
-        <v>3.454522132873535</v>
+        <v>6.209219932556152</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6215,7 +6215,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D357">
-        <v>4.629985332489014</v>
+        <v>6.20112419128418</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6229,7 +6229,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D358">
-        <v>1.233011484146118</v>
+        <v>3.57668662071228</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6243,7 +6243,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D359">
-        <v>2.261624574661255</v>
+        <v>2.0903000831604</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6257,7 +6257,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D360">
-        <v>0.9412268400192261</v>
+        <v>0.7595338821411133</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6271,7 +6271,7 @@
         <v>4.5</v>
       </c>
       <c r="D361">
-        <v>2.35596227645874</v>
+        <v>2.229002714157104</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6285,7 +6285,7 @@
         <v>2.5</v>
       </c>
       <c r="D362">
-        <v>2.190705299377441</v>
+        <v>2.148980855941772</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6299,7 +6299,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D363">
-        <v>3.344635486602783</v>
+        <v>3.403065919876099</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6313,7 +6313,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D364">
-        <v>2.246192455291748</v>
+        <v>4.922940254211426</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6327,7 +6327,7 @@
         <v>12.89999961853027</v>
       </c>
       <c r="D365">
-        <v>2.917545318603516</v>
+        <v>4.799377918243408</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6341,7 +6341,7 @@
         <v>2.5</v>
       </c>
       <c r="D366">
-        <v>2.403045654296875</v>
+        <v>2.247107982635498</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6355,7 +6355,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D367">
-        <v>1.347824335098267</v>
+        <v>2.020380973815918</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6369,7 +6369,7 @@
         <v>11.69999980926514</v>
       </c>
       <c r="D368">
-        <v>5.069153785705566</v>
+        <v>9.601772308349609</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6383,7 +6383,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D369">
-        <v>0.9199919104576111</v>
+        <v>1.267357349395752</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -6397,7 +6397,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D370">
-        <v>4.272466659545898</v>
+        <v>4.9971604347229</v>
       </c>
     </row>
     <row r="371" spans="1:4">
@@ -6411,7 +6411,7 @@
         <v>3.5</v>
       </c>
       <c r="D371">
-        <v>3.038270711898804</v>
+        <v>4.302481174468994</v>
       </c>
     </row>
     <row r="372" spans="1:4">
@@ -6425,7 +6425,7 @@
         <v>0.5</v>
       </c>
       <c r="D372">
-        <v>1.210762977600098</v>
+        <v>1.297454953193665</v>
       </c>
     </row>
     <row r="373" spans="1:4">
@@ -6439,7 +6439,7 @@
         <v>2.900000095367432</v>
       </c>
       <c r="D373">
-        <v>2.504557847976685</v>
+        <v>2.454046487808228</v>
       </c>
     </row>
     <row r="374" spans="1:4">
@@ -6453,7 +6453,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D374">
-        <v>1.215906858444214</v>
+        <v>1.359291553497314</v>
       </c>
     </row>
     <row r="375" spans="1:4">
@@ -6467,7 +6467,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D375">
-        <v>2.875949859619141</v>
+        <v>3.115673303604126</v>
       </c>
     </row>
     <row r="376" spans="1:4">
@@ -6481,7 +6481,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D376">
-        <v>1.301214456558228</v>
+        <v>1.329920887947083</v>
       </c>
     </row>
     <row r="377" spans="1:4">
@@ -6495,7 +6495,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D377">
-        <v>0.9588769674301147</v>
+        <v>0.8133918046951294</v>
       </c>
     </row>
     <row r="378" spans="1:4">
@@ -6509,7 +6509,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D378">
-        <v>3.025733947753906</v>
+        <v>2.316524267196655</v>
       </c>
     </row>
     <row r="379" spans="1:4">
@@ -6523,7 +6523,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D379">
-        <v>2.736652851104736</v>
+        <v>2.524289131164551</v>
       </c>
     </row>
     <row r="380" spans="1:4">
@@ -6537,7 +6537,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D380">
-        <v>1.689790964126587</v>
+        <v>2.410566091537476</v>
       </c>
     </row>
     <row r="381" spans="1:4">
@@ -6551,7 +6551,7 @@
         <v>2</v>
       </c>
       <c r="D381">
-        <v>1.113088369369507</v>
+        <v>1.333670854568481</v>
       </c>
     </row>
     <row r="382" spans="1:4">
@@ -6565,7 +6565,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D382">
-        <v>1.291894555091858</v>
+        <v>1.655561923980713</v>
       </c>
     </row>
     <row r="383" spans="1:4">
@@ -6579,7 +6579,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D383">
-        <v>1.026469707489014</v>
+        <v>1.578026294708252</v>
       </c>
     </row>
     <row r="384" spans="1:4">
@@ -6593,7 +6593,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D384">
-        <v>2.091744899749756</v>
+        <v>2.982221841812134</v>
       </c>
     </row>
     <row r="385" spans="1:4">
@@ -6607,7 +6607,7 @@
         <v>3.5</v>
       </c>
       <c r="D385">
-        <v>1.029579877853394</v>
+        <v>2.754652261734009</v>
       </c>
     </row>
     <row r="386" spans="1:4">
@@ -6621,7 +6621,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D386">
-        <v>2.008288860321045</v>
+        <v>2.734500408172607</v>
       </c>
     </row>
     <row r="387" spans="1:4">
@@ -6635,7 +6635,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D387">
-        <v>3.378755569458008</v>
+        <v>3.21934962272644</v>
       </c>
     </row>
     <row r="388" spans="1:4">
@@ -6649,7 +6649,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D388">
-        <v>1.026020169258118</v>
+        <v>0.772658109664917</v>
       </c>
     </row>
     <row r="389" spans="1:4">
@@ -6663,7 +6663,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D389">
-        <v>1.862919330596924</v>
+        <v>2.18895435333252</v>
       </c>
     </row>
     <row r="390" spans="1:4">
@@ -6677,7 +6677,7 @@
         <v>2.5</v>
       </c>
       <c r="D390">
-        <v>1.947150945663452</v>
+        <v>2.296398878097534</v>
       </c>
     </row>
     <row r="391" spans="1:4">
@@ -6691,7 +6691,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D391">
-        <v>0.9878473281860352</v>
+        <v>0.7852894067764282</v>
       </c>
     </row>
     <row r="392" spans="1:4">
@@ -6705,7 +6705,7 @@
         <v>1.5</v>
       </c>
       <c r="D392">
-        <v>0.928106963634491</v>
+        <v>0.7689189910888672</v>
       </c>
     </row>
     <row r="393" spans="1:4">
@@ -6719,7 +6719,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D393">
-        <v>2.051541090011597</v>
+        <v>2.408776044845581</v>
       </c>
     </row>
     <row r="394" spans="1:4">
@@ -6733,7 +6733,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D394">
-        <v>0.9344717264175415</v>
+        <v>1.32280969619751</v>
       </c>
     </row>
     <row r="395" spans="1:4">
@@ -6747,7 +6747,7 @@
         <v>1.5</v>
       </c>
       <c r="D395">
-        <v>2.471963405609131</v>
+        <v>2.397539854049683</v>
       </c>
     </row>
     <row r="396" spans="1:4">
@@ -6761,7 +6761,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D396">
-        <v>0.9835857152938843</v>
+        <v>0.7672684788703918</v>
       </c>
     </row>
     <row r="397" spans="1:4">
@@ -6775,7 +6775,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D397">
-        <v>2.990628957748413</v>
+        <v>2.982123136520386</v>
       </c>
     </row>
     <row r="398" spans="1:4">
@@ -6789,7 +6789,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D398">
-        <v>3.10062575340271</v>
+        <v>2.595734357833862</v>
       </c>
     </row>
     <row r="399" spans="1:4">
@@ -6803,7 +6803,7 @@
         <v>1</v>
       </c>
       <c r="D399">
-        <v>1.250959157943726</v>
+        <v>1.368671178817749</v>
       </c>
     </row>
     <row r="400" spans="1:4">
@@ -6817,7 +6817,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D400">
-        <v>3.460389852523804</v>
+        <v>2.841764688491821</v>
       </c>
     </row>
     <row r="401" spans="1:4">
@@ -6831,7 +6831,7 @@
         <v>4</v>
       </c>
       <c r="D401">
-        <v>3.591031789779663</v>
+        <v>2.887244701385498</v>
       </c>
     </row>
     <row r="402" spans="1:4">
@@ -6845,7 +6845,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D402">
-        <v>1.289355754852295</v>
+        <v>1.278073072433472</v>
       </c>
     </row>
     <row r="403" spans="1:4">
@@ -6859,7 +6859,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D403">
-        <v>3.269706726074219</v>
+        <v>1.198980689048767</v>
       </c>
     </row>
     <row r="404" spans="1:4">
@@ -6873,7 +6873,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D404">
-        <v>1.978546380996704</v>
+        <v>2.254916667938232</v>
       </c>
     </row>
     <row r="405" spans="1:4">
@@ -6887,7 +6887,7 @@
         <v>1.200000047683716</v>
       </c>
       <c r="D405">
-        <v>0.9571560621261597</v>
+        <v>1.020295143127441</v>
       </c>
     </row>
     <row r="406" spans="1:4">
@@ -6901,7 +6901,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D406">
-        <v>1.834230184555054</v>
+        <v>2.498708963394165</v>
       </c>
     </row>
     <row r="407" spans="1:4">
@@ -6915,7 +6915,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D407">
-        <v>1.374590158462524</v>
+        <v>1.33979594707489</v>
       </c>
     </row>
     <row r="408" spans="1:4">
@@ -6929,7 +6929,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D408">
-        <v>2.699826717376709</v>
+        <v>3.217514753341675</v>
       </c>
     </row>
     <row r="409" spans="1:4">
@@ -6943,7 +6943,7 @@
         <v>4.5</v>
       </c>
       <c r="D409">
-        <v>1.428411602973938</v>
+        <v>1.396957874298096</v>
       </c>
     </row>
     <row r="410" spans="1:4">
@@ -6957,7 +6957,7 @@
         <v>4.199999809265137</v>
       </c>
       <c r="D410">
-        <v>0.9138454794883728</v>
+        <v>1.331576347351074</v>
       </c>
     </row>
     <row r="411" spans="1:4">
@@ -6971,7 +6971,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D411">
-        <v>1.252529978752136</v>
+        <v>1.186732769012451</v>
       </c>
     </row>
     <row r="412" spans="1:4">
@@ -6985,7 +6985,7 @@
         <v>6.5</v>
       </c>
       <c r="D412">
-        <v>4.086387634277344</v>
+        <v>1.993460655212402</v>
       </c>
     </row>
     <row r="413" spans="1:4">
@@ -6999,7 +6999,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D413">
-        <v>3.138401746749878</v>
+        <v>3.623869657516479</v>
       </c>
     </row>
     <row r="414" spans="1:4">
@@ -7013,7 +7013,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D414">
-        <v>1.918419241905212</v>
+        <v>2.891839742660522</v>
       </c>
     </row>
     <row r="415" spans="1:4">
@@ -7027,7 +7027,7 @@
         <v>3.5</v>
       </c>
       <c r="D415">
-        <v>2.408704280853271</v>
+        <v>2.747887372970581</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -7041,7 +7041,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D416">
-        <v>7.571111679077148</v>
+        <v>10.52770042419434</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -7055,7 +7055,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D417">
-        <v>3.206186771392822</v>
+        <v>4.402433395385742</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -7069,7 +7069,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D418">
-        <v>2.084935903549194</v>
+        <v>2.407519817352295</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -7083,7 +7083,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D419">
-        <v>0.9539636373519897</v>
+        <v>0.7829638123512268</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -7097,7 +7097,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D420">
-        <v>1.121022582054138</v>
+        <v>1.573027491569519</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -7111,7 +7111,7 @@
         <v>4.599999904632568</v>
       </c>
       <c r="D421">
-        <v>2.870542287826538</v>
+        <v>2.866305828094482</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -7125,7 +7125,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D422">
-        <v>2.312146663665771</v>
+        <v>2.006261825561523</v>
       </c>
     </row>
     <row r="423" spans="1:4">
@@ -7139,7 +7139,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D423">
-        <v>2.997967720031738</v>
+        <v>3.805139541625977</v>
       </c>
     </row>
     <row r="424" spans="1:4">
@@ -7153,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="D424">
-        <v>0.9666095376014709</v>
+        <v>0.7832521796226501</v>
       </c>
     </row>
     <row r="425" spans="1:4">
@@ -7167,7 +7167,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D425">
-        <v>0.9697732925415039</v>
+        <v>0.8129128217697144</v>
       </c>
     </row>
     <row r="426" spans="1:4">
@@ -7181,7 +7181,7 @@
         <v>5</v>
       </c>
       <c r="D426">
-        <v>3.086743831634521</v>
+        <v>2.850601434707642</v>
       </c>
     </row>
     <row r="427" spans="1:4">
@@ -7195,7 +7195,7 @@
         <v>0.5</v>
       </c>
       <c r="D427">
-        <v>1.179832696914673</v>
+        <v>1.16744601726532</v>
       </c>
     </row>
     <row r="428" spans="1:4">
@@ -7209,7 +7209,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D428">
-        <v>1.165441036224365</v>
+        <v>1.310606479644775</v>
       </c>
     </row>
     <row r="429" spans="1:4">
@@ -7223,7 +7223,7 @@
         <v>7</v>
       </c>
       <c r="D429">
-        <v>3.142734050750732</v>
+        <v>3.201009511947632</v>
       </c>
     </row>
     <row r="430" spans="1:4">
@@ -7237,7 +7237,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D430">
-        <v>3.353610754013062</v>
+        <v>2.921225309371948</v>
       </c>
     </row>
     <row r="431" spans="1:4">
@@ -7251,7 +7251,7 @@
         <v>0.5</v>
       </c>
       <c r="D431">
-        <v>1.48051381111145</v>
+        <v>1.347940921783447</v>
       </c>
     </row>
     <row r="432" spans="1:4">
@@ -7265,7 +7265,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D432">
-        <v>2.711027145385742</v>
+        <v>2.313036203384399</v>
       </c>
     </row>
     <row r="433" spans="1:4">
@@ -7279,7 +7279,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D433">
-        <v>1.407107830047607</v>
+        <v>1.332703351974487</v>
       </c>
     </row>
     <row r="434" spans="1:4">
@@ -7293,7 +7293,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D434">
-        <v>1.117550134658813</v>
+        <v>1.464963912963867</v>
       </c>
     </row>
     <row r="435" spans="1:4">
@@ -7307,7 +7307,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D435">
-        <v>2.987291812896729</v>
+        <v>5.6043381690979</v>
       </c>
     </row>
     <row r="436" spans="1:4">
@@ -7321,7 +7321,7 @@
         <v>0.5</v>
       </c>
       <c r="D436">
-        <v>3.107212543487549</v>
+        <v>2.494866609573364</v>
       </c>
     </row>
     <row r="437" spans="1:4">
@@ -7335,7 +7335,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D437">
-        <v>0.9815638661384583</v>
+        <v>0.8146070837974548</v>
       </c>
     </row>
     <row r="438" spans="1:4">
@@ -7349,7 +7349,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D438">
-        <v>1.065646409988403</v>
+        <v>0.9560690522193909</v>
       </c>
     </row>
     <row r="439" spans="1:4">
@@ -7363,7 +7363,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D439">
-        <v>2.468252658843994</v>
+        <v>1.35503625869751</v>
       </c>
     </row>
     <row r="440" spans="1:4">
@@ -7377,7 +7377,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D440">
-        <v>1.265469670295715</v>
+        <v>1.29943835735321</v>
       </c>
     </row>
     <row r="441" spans="1:4">
@@ -7391,7 +7391,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D441">
-        <v>0.9332311153411865</v>
+        <v>1.316584348678589</v>
       </c>
     </row>
     <row r="442" spans="1:4">
@@ -7405,7 +7405,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D442">
-        <v>0.9621696472167969</v>
+        <v>0.7624891996383667</v>
       </c>
     </row>
     <row r="443" spans="1:4">
@@ -7419,7 +7419,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D443">
-        <v>3.600398540496826</v>
+        <v>5.517825603485107</v>
       </c>
     </row>
     <row r="444" spans="1:4">
@@ -7433,7 +7433,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D444">
-        <v>2.914612293243408</v>
+        <v>3.519787311553955</v>
       </c>
     </row>
     <row r="445" spans="1:4">
@@ -7447,7 +7447,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D445">
-        <v>2.445804595947266</v>
+        <v>1.509590864181519</v>
       </c>
     </row>
     <row r="446" spans="1:4">
@@ -7461,7 +7461,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D446">
-        <v>1.899281024932861</v>
+        <v>2.317247629165649</v>
       </c>
     </row>
     <row r="447" spans="1:4">
@@ -7475,7 +7475,7 @@
         <v>1.600000023841858</v>
       </c>
       <c r="D447">
-        <v>1.141168713569641</v>
+        <v>0.770536482334137</v>
       </c>
     </row>
     <row r="448" spans="1:4">
@@ -7489,7 +7489,7 @@
         <v>6.800000190734863</v>
       </c>
       <c r="D448">
-        <v>4.492676734924316</v>
+        <v>6.401994705200195</v>
       </c>
     </row>
   </sheetData>
